--- a/data/trans_camb/P6902-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6902-Clase-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 0,89</t>
+          <t>-31,7; 2,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,33; 11,31</t>
+          <t>-19,6; 13,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 28,98</t>
+          <t>3,2; 28,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 21,79</t>
+          <t>-12,35; 21,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 12,45</t>
+          <t>-25,33; 13,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 24,11</t>
+          <t>-7,23; 23,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 6,08</t>
+          <t>-17,63; 7,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 8,11</t>
+          <t>-17,87; 6,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 20,5</t>
+          <t>0,95; 19,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,85; 1,34</t>
+          <t>-38,34; 2,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 15,87</t>
+          <t>-23,92; 19,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 42,98</t>
+          <t>4,09; 43,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 33,2</t>
+          <t>-14,31; 32,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 19,49</t>
+          <t>-29,87; 18,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 38,27</t>
+          <t>-8,23; 37,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 8,41</t>
+          <t>-21,83; 11,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 11,56</t>
+          <t>-22,19; 9,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 29,79</t>
+          <t>1,17; 28,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 36,14</t>
+          <t>-9,4; 35,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 27,58</t>
+          <t>-20,03; 28,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 47,85</t>
+          <t>10,72; 50,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 16,78</t>
+          <t>-35,47; 14,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 27,41</t>
+          <t>-11,0; 28,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 30,92</t>
+          <t>-4,4; 28,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 19,6</t>
+          <t>-15,92; 17,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 23,14</t>
+          <t>-11,12; 23,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 35,73</t>
+          <t>7,87; 35,06</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 87,5</t>
+          <t>-12,93; 89,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 69,28</t>
+          <t>-30,33; 73,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,58; 115,08</t>
+          <t>16,35; 124,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,9; 27,89</t>
+          <t>-48,4; 23,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 48,29</t>
+          <t>-14,77; 48,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 54,74</t>
+          <t>-5,47; 49,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 36,7</t>
+          <t>-22,77; 33,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 43,12</t>
+          <t>-15,73; 44,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,08; 69,32</t>
+          <t>11,31; 66,57</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 3,78</t>
+          <t>-27,39; 6,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-33,1; -3,29</t>
+          <t>-32,24; -0,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 11,09</t>
+          <t>-22,07; 12,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 45,27</t>
+          <t>-16,83; 44,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 74,02</t>
+          <t>-2,81; 71,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 51,45</t>
+          <t>-13,05; 49,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 8,16</t>
+          <t>-19,62; 7,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 4,85</t>
+          <t>-25,98; 3,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 12,23</t>
+          <t>-15,05; 13,2</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,63; 8,98</t>
+          <t>-45,79; 15,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,89; -4,32</t>
+          <t>-57,92; -0,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,83; 23,28</t>
+          <t>-39,49; 25,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 410,68</t>
+          <t>-39,15; 358,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 774,9</t>
+          <t>-8,82; 645,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 498,82</t>
+          <t>-29,76; 408,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,25; 20,43</t>
+          <t>-34,49; 18,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,2; 10,77</t>
+          <t>-46,68; 8,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 28,14</t>
+          <t>-27,38; 32,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 22,33</t>
+          <t>-0,45; 22,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 23,02</t>
+          <t>0,82; 22,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,67; 34,68</t>
+          <t>11,57; 34,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 14,74</t>
+          <t>-20,19; 19,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 26,67</t>
+          <t>-9,07; 26,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 32,87</t>
+          <t>-0,36; 31,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 18,43</t>
+          <t>-0,31; 18,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 22,02</t>
+          <t>4,36; 22,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,33; 32,88</t>
+          <t>14,75; 32,89</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 84,59</t>
+          <t>-1,11; 83,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 86,67</t>
+          <t>2,96; 85,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30,34; 130,11</t>
+          <t>32,58; 127,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,11; 36,4</t>
+          <t>-33,53; 51,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 70,85</t>
+          <t>-14,72; 71,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 92,29</t>
+          <t>-0,68; 86,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 60,16</t>
+          <t>-1,34; 59,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,18; 71,36</t>
+          <t>11,27; 75,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,83; 110,98</t>
+          <t>36,82; 109,05</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 21,78</t>
+          <t>-15,94; 22,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 15,88</t>
+          <t>-14,79; 16,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 40,12</t>
+          <t>1,84; 39,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,82; 44,87</t>
+          <t>6,06; 43,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 31,77</t>
+          <t>-4,04; 30,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 30,01</t>
+          <t>-16,64; 30,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 28,67</t>
+          <t>1,4; 30,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 16,3</t>
+          <t>-5,89; 18,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 28,32</t>
+          <t>-7,27; 29,51</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-48,45; 126,93</t>
+          <t>-50,92; 132,18</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,37; 99,9</t>
+          <t>-42,7; 97,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4,74; 247,45</t>
+          <t>3,4; 230,32</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16,37; 230,9</t>
+          <t>10,64; 216,92</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 155,44</t>
+          <t>-13,52; 141,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,57; 126,6</t>
+          <t>-43,62; 125,63</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,25; 135,75</t>
+          <t>3,85; 141,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 75,91</t>
+          <t>-16,98; 90,1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 124,61</t>
+          <t>-19,71; 131,49</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,45</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18,43</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,2</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,24</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,12</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,04</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,2</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,74; 10,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,96; 6,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,14; 25,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,92; 16,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,21; 19,33</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,69; 19,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,8; 11,08</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,51; 9,97</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,03; 21,16</t>
         </is>
       </c>
     </row>
@@ -1810,47 +1810,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -1863,282 +1863,65 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,34; 25,52</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,57; 16,45</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,74; 63,93</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,75; 34,81</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,39; 41,95</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,77; 42,38</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,52; 25,82</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,23; 22,95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,01; 47,67</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>3,45</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>18,43</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>6,2</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>9,24</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>9,12</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>5,19</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4,04</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>15,2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>-3,32; 10,75</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>-7,17; 6,81</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>11,83; 25,95</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>-3,15; 15,3</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>-1,21; 18,09</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-10,04; 18,71</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-0,68; 10,81</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-1,91; 9,6</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>4,98; 21,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>42,44%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>12,07%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>17,99%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>17,76%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>33,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>-7,2; 25,81</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>-15,62; 16,88</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>25,51; 64,31</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>-5,97; 33,11</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>-2,09; 39,78</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-15,54; 39,16</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-1,37; 25,55</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-3,76; 22,4</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>12,08; 48,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A24:A27"/>

--- a/data/trans_camb/P6902-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6902-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16,29</t>
+          <t>17,45</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,66</t>
+          <t>6,13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,85</t>
+          <t>11,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 2,46</t>
+          <t>-30,06; 1,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 13,44</t>
+          <t>-19,68; 12,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 28,13</t>
+          <t>5,64; 28,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 21,5</t>
+          <t>-11,46; 22,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 13,4</t>
+          <t>-24,82; 11,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 23,25</t>
+          <t>-7,45; 21,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 7,65</t>
+          <t>-17,94; 6,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 6,78</t>
+          <t>-16,18; 8,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 19,85</t>
+          <t>2,82; 21,18</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,34; 2,2</t>
+          <t>-38,1; 0,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,92; 19,3</t>
+          <t>-24,2; 17,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 43,13</t>
+          <t>7,27; 43,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 32,36</t>
+          <t>-13,1; 35,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,87; 18,55</t>
+          <t>-29,45; 16,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 37,68</t>
+          <t>-8,88; 32,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 11,14</t>
+          <t>-22,24; 9,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 9,17</t>
+          <t>-20,28; 11,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 28,15</t>
+          <t>3,53; 30,97</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30,59</t>
+          <t>30,25</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,04</t>
+          <t>13,72</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>22,07</t>
+          <t>22,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 35,33</t>
+          <t>-10,89; 36,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 28,83</t>
+          <t>-21,89; 27,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,72; 50,02</t>
+          <t>9,69; 48,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 14,35</t>
+          <t>-37,16; 14,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 28,32</t>
+          <t>-13,25; 28,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 28,47</t>
+          <t>-3,89; 30,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 17,81</t>
+          <t>-14,79; 18,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 23,61</t>
+          <t>-10,42; 22,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,87; 35,06</t>
+          <t>8,54; 36,58</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 89,81</t>
+          <t>-16,22; 89,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,33; 73,31</t>
+          <t>-33,09; 61,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,35; 124,47</t>
+          <t>14,07; 123,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,4; 23,26</t>
+          <t>-47,98; 23,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 48,29</t>
+          <t>-17,34; 49,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 49,79</t>
+          <t>-4,14; 56,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 33,23</t>
+          <t>-21,16; 34,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 44,28</t>
+          <t>-15,9; 41,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,31; 66,57</t>
+          <t>12,24; 73,71</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-5,71</t>
+          <t>-3,3</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>24,45</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 6,97</t>
+          <t>-26,13; 4,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-32,24; -0,18</t>
+          <t>-33,31; -2,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 12,25</t>
+          <t>-19,88; 14,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 44,48</t>
+          <t>-13,71; 47,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 71,43</t>
+          <t>-1,89; 73,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 49,68</t>
+          <t>-7,09; 53,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 7,17</t>
+          <t>-19,3; 7,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 3,45</t>
+          <t>-25,84; 4,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 13,2</t>
+          <t>-14,58; 15,34</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-10,96%</t>
+          <t>-6,34%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-2,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,79; 15,1</t>
+          <t>-44,49; 9,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,92; -0,64</t>
+          <t>-57,82; -5,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,49; 25,53</t>
+          <t>-36,44; 29,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,15; 358,29</t>
+          <t>-30,3; 660,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 645,77</t>
+          <t>-15,53; 624,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,76; 408,1</t>
+          <t>-17,81; 700,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 18,09</t>
+          <t>-35,3; 18,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 8,83</t>
+          <t>-48,08; 10,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 32,84</t>
+          <t>-26,62; 36,11</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23,19</t>
+          <t>23,93</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,76</t>
+          <t>15,77</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24,36</t>
+          <t>24,6</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 22,04</t>
+          <t>0,95; 21,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 22,8</t>
+          <t>0,95; 22,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,57; 34,71</t>
+          <t>11,89; 34,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 19,72</t>
+          <t>-21,23; 16,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 26,85</t>
+          <t>-9,63; 26,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 31,65</t>
+          <t>0,05; 30,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 18,52</t>
+          <t>-0,26; 20,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 22,46</t>
+          <t>4,7; 22,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,75; 32,89</t>
+          <t>16,39; 32,48</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,74%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 83,39</t>
+          <t>1,25; 78,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,96; 85,52</t>
+          <t>2,51; 86,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,58; 127,99</t>
+          <t>32,32; 126,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,53; 51,92</t>
+          <t>-35,56; 42,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 71,06</t>
+          <t>-14,78; 75,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 86,07</t>
+          <t>1,02; 81,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 59,31</t>
+          <t>-1,22; 65,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,27; 75,62</t>
+          <t>11,5; 73,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>36,82; 109,05</t>
+          <t>40,64; 106,3</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21,02</t>
+          <t>17,93</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,76</t>
+          <t>27,0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14,44</t>
+          <t>23,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 22,23</t>
+          <t>-13,61; 23,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 16,26</t>
+          <t>-15,9; 16,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,84; 39,82</t>
+          <t>-0,16; 35,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,06; 43,93</t>
+          <t>5,89; 43,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 30,85</t>
+          <t>-5,29; 30,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 30,26</t>
+          <t>11,94; 40,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 30,39</t>
+          <t>0,09; 29,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 18,56</t>
+          <t>-6,98; 16,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 29,51</t>
+          <t>12,51; 34,29</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,92; 132,18</t>
+          <t>-42,75; 139,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-42,7; 97,52</t>
+          <t>-47,47; 103,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3,4; 230,32</t>
+          <t>-1,9; 213,94</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10,64; 216,92</t>
+          <t>16,34; 234,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 141,95</t>
+          <t>-13,16; 156,56</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 125,63</t>
+          <t>29,06; 216,09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,85; 141,24</t>
+          <t>-2,01; 138,14</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 90,1</t>
+          <t>-21,59; 81,16</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 131,49</t>
+          <t>36,31; 167,72</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18,43</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,12</t>
+          <t>16,05</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15,2</t>
+          <t>18,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 10,52</t>
+          <t>-3,76; 10,4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 6,68</t>
+          <t>-7,6; 7,24</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11,14; 25,33</t>
+          <t>10,54; 24,81</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 16,13</t>
+          <t>-4,02; 15,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 19,33</t>
+          <t>-0,47; 18,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 19,39</t>
+          <t>8,36; 23,3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 11,08</t>
+          <t>-0,27; 10,73</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 9,97</t>
+          <t>-2,02; 10,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,03; 21,16</t>
+          <t>12,87; 23,8</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 25,52</t>
+          <t>-8,31; 25,86</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 16,45</t>
+          <t>-16,43; 17,69</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23,74; 63,93</t>
+          <t>21,72; 61,13</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 34,81</t>
+          <t>-7,05; 34,04</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 41,95</t>
+          <t>-0,81; 40,37</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 42,38</t>
+          <t>14,41; 52,12</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 25,82</t>
+          <t>-0,8; 25,35</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 22,95</t>
+          <t>-4,13; 23,7</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>11,01; 47,67</t>
+          <t>26,28; 55,09</t>
         </is>
       </c>
     </row>
